--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -1274,47 +1274,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>31.10.2026</t>
+          <t>01.11.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
+          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Orange, Ringerike 2, Kongsberg/Tønsberg</t>
+          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1331,42 +1331,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
+          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
+          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1383,42 +1383,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U8 Turnering — Bugården ishall</t>
+          <t>U9 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
+          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
+          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1435,42 +1435,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U9 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
+          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
+          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1482,12 +1482,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01.11.2026</t>
+          <t>07.11.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1539,42 +1539,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
+          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1591,42 +1591,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>JU8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1643,42 +1643,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07.11.2026</t>
+          <t>08.11.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
+          <t>Ringerike, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
+          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1747,42 +1747,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>JU10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
+          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1799,42 +1799,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
+          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U11 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
+          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1903,42 +1903,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
+          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
+          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1950,47 +1950,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
+          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2007,42 +2007,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
+          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
+          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2111,42 +2111,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U9 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2163,42 +2163,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>17:20</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>U11</t>
@@ -2240,17 +2240,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
+          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2267,42 +2267,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
+          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
+          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2314,47 +2314,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>15.11.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
+          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
+          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2371,42 +2371,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
+          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
+          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
+          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
+          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U12 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2542,27 +2542,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
+          <t>Jar, Jutul, Holmen, Frisk Asker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
+          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2574,47 +2574,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15.11.2026</t>
+          <t>21.11.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Holmen, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2631,42 +2631,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
+          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2683,42 +2683,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
+          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
+          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2735,42 +2735,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U9 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
+          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2787,42 +2787,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
+          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2839,42 +2839,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>U8 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2891,42 +2891,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U8 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
+          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
+          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2938,47 +2938,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21.11.2026</t>
+          <t>22.11.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
+          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
+          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
+          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
+          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3047,42 +3047,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
+          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
+          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3099,42 +3099,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
+          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
+          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,42 +3151,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3203,42 +3203,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Kongsberghallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
+          <t>Jar, Frisk Asker, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
+          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3255,42 +3255,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Jutul</t>
+          <t>Jutul, Frisk Asker, Holmen, Jar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
+          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3302,47 +3302,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Ringerike, Jar, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
+          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Jutul</t>
+          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
+          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3411,42 +3411,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
+          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
+          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3515,42 +3515,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
+          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
+          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3567,42 +3567,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
+          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3614,22 +3614,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>29.11.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3639,22 +3639,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3671,42 +3671,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3723,42 +3723,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
+          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3775,42 +3775,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
+          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
+          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3827,42 +3827,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U8 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
+          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
+          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3879,42 +3879,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
+          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3926,12 +3926,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>29.11.2026</t>
+          <t>05.12.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
+          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3978,47 +3978,47 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>05.12.2026</t>
+          <t>06.12.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>U8 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Tønsberg, Frisk Asker, Holmen, Jar, Jutul, Kongsberg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
+          <t>Tønsberg, Frisk Asker 3, Holmen Hockey Rød, Jar Svart, Jutul Gul, Holmen Hockey Sort, Frisk Asker 5, Kongsberg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4030,27 +4030,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06.12.2026</t>
+          <t>12.12.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U8 Turnering — Tonsberghallen</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4060,17 +4060,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tønsberg, Frisk Asker, Holmen, Jar, Jutul, Kongsberg</t>
+          <t>Jutul, Frisk Asker, Holmen, Tønsberg, Ringerike, Jar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tønsberg, Frisk Asker 3, Holmen Hockey Rød, Jar Svart, Jutul Gul, Holmen Hockey Sort, Frisk Asker 5, Kongsberg</t>
+          <t>Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Frisk Asker 3, Jar Blå</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4087,42 +4087,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Holmen, Tønsberg, Ringerike, Jar</t>
+          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Frisk Asker 3, Jar Blå</t>
+          <t>Skien, Frisk Asker Orange, Ringerike 2, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -1222,47 +1222,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31.10.2026</t>
+          <t>01.11.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U9 Turnering — Bugården ishall</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Frisk Asker, Skien, Holmen, Kongsberg, Ringerike, Tønsberg</t>
+          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sandefjord, Frisk Asker 3, Frisk Asker 1, Skien, Holmen Hockey Sort, Kongsberg, Ringerike 1, Tønsberg</t>
+          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1279,42 +1279,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Tønsberg</t>
+          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Jar Gul, Frisk Asker 4, Jar Blå, Tønsberg Hvit, Frisk Asker 1</t>
+          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1331,42 +1331,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U8 Turnering — Bugården ishall</t>
+          <t>U9 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Frisk Asker, Holmen, Jar, Jutul, Ringerike</t>
+          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sandefjord, Frisk Asker 5, Holmen Hockey Rød, Jar Rød, Jutul Hvit, Jutul Gul, Ringerike 2, Holmen Hockey Hvit</t>
+          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1383,42 +1383,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U9 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Holmen, Jar, Jutul, Tønsberg, Kongsberg</t>
+          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker 3, Holmen Hockey Hvit, Jar Hvit, Jutul Rød, Frisk Asker 4, Tønsberg, Kongsberg</t>
+          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01.11.2026</t>
+          <t>07.11.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1445,17 +1445,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jar Blå, Tønsberg Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1487,42 +1487,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Grønn, Holmen Hockey Rød, Ringerike 4, Jutul Grønn, Frisk Asker 3</t>
+          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1539,42 +1539,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>JU8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ringerike, Tønsberg, Jar, Holmen, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ringerike Svart, Tønsberg Hvit, Jar Svart, Holmen Hockey Rød, Frisk Asker 2, Jutul Grønn</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1591,42 +1591,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07.11.2026</t>
+          <t>08.11.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Frisk Asker, Holmen</t>
+          <t>Ringerike, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Frisk Asker 3, Holmen Hockey Rød</t>
+          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1695,42 +1695,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>JU10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul</t>
+          <t>Frisk Asker, Jar, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
+          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1747,42 +1747,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Rød, Ringerike 1, Skien, Jar Blå</t>
+          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1799,42 +1799,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U11 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Jar Hvit, Frisk Asker 4, Jar Lilla, Kongsberg, Tønsberg Grå, Jar Oransje</t>
+          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Tønsberg</t>
+          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Jar Rød, Holmen Hockey Rød, Holmen Hockey Blå, Ringerike 3, Tønsberg</t>
+          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1898,47 +1898,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Kongsberg, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Svart, Kongsberg, Frisk Asker 2</t>
+          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1955,42 +1955,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike</t>
+          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Holmen Hockey Hvit, Ringerike 3, Jar Gul, Frisk Asker 5</t>
+          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Holmen, Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Skien, Jar Svart, Frisk Asker 4, Frisk Asker 1, Jutul Rød, Ringerike 1, Jar Rød</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2059,42 +2059,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U9 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
+          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2111,42 +2111,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Ringerike, Jutul</t>
+          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Frisk Asker 6, Jar Svart, Holmen Hockey Blå, Ringerike 2, Jutul Rød, Jar Rød</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2163,24 +2163,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>17:20</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>U11</t>
@@ -2188,17 +2188,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Sandefjord Penguins, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Rød, Sandefjord, Frisk Asker 4, Jutul Rød</t>
+          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2215,42 +2215,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Ringerike</t>
+          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jar Grønn, Jar Rød, Frisk Asker 1, Holmen Hockey Rød, Frisk Asker 2, Ringerike Gul</t>
+          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2262,47 +2262,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>15.11.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jutul, Jar, Tønsberg</t>
+          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jutul Grønn, Jar Hvit, Tønsberg Rød</t>
+          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2319,42 +2319,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike, Kongsberg/Tønsberg</t>
+          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Svart, Ringerike 1, Kongsberg/Tønsberg</t>
+          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Jar Rød, Holmen Hockey Hvit, Ringerike 2, Frisk Asker 3</t>
+          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2423,22 +2423,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
+          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tønsberg Grå, Jar Svart, Ringerike 1, Frisk Asker 2</t>
+          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U12 Turnering — Kongsberghallen</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2490,27 +2490,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Tønsberg, Jutul</t>
+          <t>Jar, Jutul, Holmen, Frisk Asker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Jar Blå, Kongsberg, Tønsberg Hvit, Jutul Rød</t>
+          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2522,47 +2522,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15.11.2026</t>
+          <t>21.11.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Holmen, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Jar Blå, Jutul Grønn, Jutul Hvit, Holmen Hockey Blå, Jar Hvit, Frisk Asker 2</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2579,42 +2579,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AVLYST: JU8 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Ringerike, Skien</t>
+          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Ringerike 1, Skien</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2631,42 +2631,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Tønsberg</t>
+          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 1, Jar Rød, Jutul Rød, Ringerike 1, Tønsberg</t>
+          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2683,42 +2683,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U9 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Jutul, Holmen, Frisk Asker, Jar, Kongsberg, Tønsberg</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jutul Grønn, Holmen Hockey Sort, Frisk Asker 2, Jar Rød, Kongsberg, Frisk Asker 4, Tønsberg</t>
+          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2735,42 +2735,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 2, Jutul/Jar Kittens, Skien</t>
+          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2787,42 +2787,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>U8 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2839,42 +2839,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U8 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Frisk Asker, Holmen, Jutul, Kongsberg, Jar</t>
+          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Hvit, Jutul Grønn, Jutul Hvit, Kongsberg, Jar Blå, Holmen Hockey Blå</t>
+          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2886,47 +2886,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21.11.2026</t>
+          <t>22.11.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Frisk Asker, Jutul, Tønsberg</t>
+          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Hvit, Frisk Asker 4, Jutul Rød, Tønsberg Grå, Jar Blå</t>
+          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jar, Tønsberg, Holmen, Jutul</t>
+          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker 2, Jar Grønn, Tønsberg, Holmen Hockey Hvit, Jutul Hvit</t>
+          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2995,42 +2995,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Jutul, Frisk Asker, Ringerike</t>
+          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Gul, Jutul Grønn, Jar Blå, Frisk Asker 6, Ringerike 4</t>
+          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3047,42 +3047,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Frisk Asker, Tønsberg, Jar, Holmen</t>
+          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Tønsberg Grå, Jar Hvit, Holmen Hockey Rød</t>
+          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3099,42 +3099,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Skien, Jutul, Frisk Asker, Holmen, Jar, Sandefjord Penguins</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Skien, Jutul Grønn, Frisk Asker 4, Holmen Hockey Sort, Jar Hvit, Jar Blå, Frisk Asker 5, Sandefjord</t>
+          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,42 +3151,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Kongsberghallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker, Ringerike</t>
+          <t>Jar, Frisk Asker, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg, Frisk Asker Svart, Ringerike 1</t>
+          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3203,42 +3203,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Jutul</t>
+          <t>Jutul, Frisk Asker, Holmen, Jar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 1, Frisk Asker 2, Holmen Hockey Hvit, Jutul Grønn, Jar Oransje</t>
+          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3250,47 +3250,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22.11.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Ringerike, Jar, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jutul Hvit, Frisk Asker 1, Holmen Hockey Hvit, Jar Rød, Frisk Asker 2, Holmen Hockey Sort, Jar Blå</t>
+          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Tønsberg, Jutul</t>
+          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jar Rød, Tønsberg Rød, Jutul Rød</t>
+          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3359,42 +3359,42 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Holmen, Ringerike, Frisk Asker</t>
+          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Jar Blå, Holmen Hockey Sort, Ringerike 1, Jar Svart, Frisk Asker 1</t>
+          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Frisk Asker, Ringerike, Jutul, Skien</t>
+          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens, Skien</t>
+          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3463,42 +3463,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
+          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Grønn, Ringerike Svart, Tønsberg Rød, Holmen Hockey Hvit, Jar Rød</t>
+          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3515,42 +3515,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Jar Svart, Tønsberg Hvit, Frisk Asker 1, Jutul Grønn</t>
+          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3562,22 +3562,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>29.11.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU8 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3587,22 +3587,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Kongsberg, Jutul</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Hvit, Jar Svart, Frisk Asker 1, Kongsberg, Jutul Rød</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3619,42 +3619,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Skien ishall</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3671,42 +3671,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jutul, Kongsberg/Tønsberg</t>
+          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Svart, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3723,42 +3723,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Holmen, Kongsberg, Frisk Asker, Tønsberg</t>
+          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Kongsberg, Frisk Asker 2, Tønsberg Grå</t>
+          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3775,42 +3775,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U8 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Ringerike, Sandefjord Penguins, Jar, Frisk Asker, Jutul, Holmen</t>
+          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Ringerike 1, Sandefjord, Jar Rød, Frisk Asker 3, Jutul Hvit, Frisk Asker 4, Holmen Hockey Blå, Jar Hvit</t>
+          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3827,42 +3827,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Sandefjord Penguins, Ringerike, Skien</t>
+          <t>Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Oransje, Frisk Asker 3, Sandefjord, Ringerike Svart, Skien</t>
+          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3874,12 +3874,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>29.11.2026</t>
+          <t>05.12.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3889,17 +3889,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 3, Holmen Hockey Rød, Jar Hvit</t>
+          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3926,47 +3926,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>05.12.2026</t>
+          <t>06.12.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>U9 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Sandefjord Penguins, Frisk Asker, Skien, Holmen, Kongsberg, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Jar Hvit, Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
+          <t>Sandefjord, Frisk Asker 3, Frisk Asker 1, Skien, Holmen Hockey Sort, Kongsberg, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -1029,12 +1029,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6427,42 +6427,42 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U11 Turnering — Bugården ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bugården ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins, Jar, Frisk Asker, Ringerike</t>
+          <t>Jar, Kongsberg, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Sandefjord, Jar Gul, Frisk Asker 3, Ringerike Svart, Frisk Asker 4, Jar Lilla</t>
+          <t>Jar Hvit, Kongsberg, Holmen Hockey Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6479,42 +6479,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Jar, Kongsberg, Holmen, Jutul</t>
+          <t>Jutul, Jar, Holmen, Kongsberg</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Jar Hvit, Kongsberg, Holmen Hockey Rød, Jutul Rød</t>
+          <t>Jutul Grønn, Jar Grønn, Holmen Hockey Sort, Holmen Hockey Hvit, Kongsberg, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6531,42 +6531,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Holmen, Kongsberg</t>
+          <t>Jar, Jutul, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jar Grønn, Holmen Hockey Sort, Holmen Hockey Hvit, Kongsberg, Holmen Hockey Blå</t>
+          <t>Jar Svart, Jutul Grønn, Frisk Asker 1, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6593,17 +6593,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Frisk Asker, Tønsberg</t>
+          <t>Jar, Jutul, Frisk Asker, Holmen, Tønsberg</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Jar Svart, Jutul Grønn, Frisk Asker 1, Tønsberg Grå</t>
+          <t>Jar Grønn, Jar Blå, Jutul Grønn, Jutul Hvit, Frisk Asker 2, Frisk Asker 3, Holmen Hockey Sort, Tønsberg</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6630,47 +6630,47 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>24.01.2027</t>
+          <t>30.01.2027</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U7 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Jar, Jutul, Frisk Asker, Holmen, Tønsberg</t>
+          <t>Frisk Asker, Kongsberg/Tønsberg, Ringerike</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Jar Grønn, Jar Blå, Jutul Grønn, Jutul Hvit, Frisk Asker 2, Frisk Asker 3, Holmen Hockey Sort, Tønsberg</t>
+          <t>Frisk Asker Svart, Frisk Asker Orange, Kongsberg/Tønsberg, Ringerike 1</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6687,42 +6687,42 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Frisk Asker, Kongsberg/Tønsberg, Ringerike</t>
+          <t>Jar, Tønsberg, Jutul, Kongsberg, Ringerike</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart, Frisk Asker Orange, Kongsberg/Tønsberg, Ringerike 1</t>
+          <t>Jar Blå, Tønsberg Hvit, Jutul Rød, Kongsberg, Ringerike Gul, Jar Oransje</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6739,42 +6739,42 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Jutul, Kongsberg, Ringerike</t>
+          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Jar Blå, Tønsberg Hvit, Jutul Rød, Kongsberg, Ringerike Gul, Jar Oransje</t>
+          <t>Tønsberg Grå, Jar Rød, Ringerike 1, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6791,42 +6791,42 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Ringerike, Frisk Asker</t>
+          <t>Jar, Holmen, Frisk Asker, Sandefjord Penguins, Jutul</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tønsberg Grå, Jar Rød, Ringerike 1, Frisk Asker 1</t>
+          <t>Jar Blå, Jar Hvit, Holmen Hockey Hvit, Frisk Asker 2, Sandefjord, Frisk Asker 3, Holmen Hockey Sort, Jutul Rød</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6843,42 +6843,42 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Frisk Asker, Sandefjord Penguins, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Tønsberg</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Jar Blå, Jar Hvit, Holmen Hockey Hvit, Frisk Asker 2, Sandefjord, Frisk Asker 3, Holmen Hockey Sort, Jutul Rød</t>
+          <t>Frisk Asker 3, Jar Svart, Holmen Hockey Rød, Tønsberg Hvit</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6895,42 +6895,42 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Tønsberg</t>
+          <t>Frisk Asker, Tønsberg, Jar, Skien</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar Svart, Holmen Hockey Rød, Tønsberg Hvit</t>
+          <t>Frisk Asker 4, Tønsberg Rød, Jar Lilla, Jar Svart, Skien, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6947,42 +6947,42 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>U11 Turnering — Tonsberghallen</t>
+          <t>U8 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Frisk Asker, Tønsberg, Jar, Skien</t>
+          <t>Holmen, Ringerike, Jar, Sandefjord Penguins, Frisk Asker, Skien</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Tønsberg Rød, Jar Lilla, Jar Svart, Skien, Tønsberg Grå</t>
+          <t>Holmen Hockey Sort, Ringerike 2, Jar Blå, Sandefjord, Frisk Asker 3, Jar Svart, Frisk Asker 2, Skien</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6994,12 +6994,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>30.01.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U8 Turnering — Askerhallen</t>
+          <t>JU10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7009,17 +7009,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Holmen, Ringerike, Jar, Sandefjord Penguins, Frisk Asker, Skien</t>
+          <t>Frisk Asker, Jar, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort, Ringerike 2, Jar Blå, Sandefjord, Frisk Asker 3, Jar Svart, Frisk Asker 2, Skien</t>
+          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Blå, Ringerike 1, Skien, Jar Hvit</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7051,42 +7051,42 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Skien</t>
+          <t>Ringerike, Frisk Asker, Jar, Holmen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange, Frisk Asker Svart, Jar Blå, Ringerike 1, Skien, Jar Hvit</t>
+          <t>Ringerike 1, Frisk Asker 4, Jar Rød, Jar Gul, Holmen Hockey Rød, Ringerike 3</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7123,22 +7123,22 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Jar, Holmen</t>
+          <t>Tønsberg, Jar, Holmen, Kongsberg, Ringerike</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Ringerike 1, Frisk Asker 4, Jar Rød, Jar Gul, Holmen Hockey Rød, Ringerike 3</t>
+          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Kongsberg, Ringerike Svart, Jar Lilla</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7155,42 +7155,42 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>U11 Turnering — Tonsberghallen</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Holmen, Kongsberg, Ringerike</t>
+          <t>Holmen, Jar, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Kongsberg, Ringerike Svart, Jar Lilla</t>
+          <t>Holmen Hockey Hvit, Jar Rød, Jutul Rød, Ringerike 2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7202,17 +7202,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>06.02.2027</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7222,27 +7222,27 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Jutul, Ringerike</t>
+          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Kongsberg</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Jar Rød, Jutul Rød, Ringerike 2</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7274,27 +7274,27 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jar, Jutul, Ringerike, Kongsberg</t>
+          <t>Jar, Frisk Asker, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 6, Jar Blå, Jutul Hvit, Ringerike 4, Kongsberg</t>
+          <t>Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7311,42 +7311,42 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Tønsberg, Jutul</t>
+          <t>Frisk Asker, Jar, Holmen, Jutul, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Jar Blå, Frisk Asker 2, Tønsberg Rød, Jutul Rød</t>
+          <t>Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7363,42 +7363,42 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>U7 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Jutul, Sandefjord Penguins</t>
+          <t>Ringerike, Holmen, Tønsberg</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar Grønn, Jar Blå, Holmen Hockey Hvit, Jar Hvit, Jutul Grønn, Sandefjord, Holmen Hockey Rød</t>
+          <t>Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7415,42 +7415,42 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>U12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Ringerike, Holmen, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Sandefjord Penguins, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Ringerike 1, Ringerike 2, Holmen Hockey Rød, Tønsberg Grå</t>
+          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Sandefjord, Jutul Rød, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7462,27 +7462,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>06.02.2027</t>
+          <t>07.02.2027</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Sandefjord Penguins, Jutul, Tønsberg</t>
+          <t>Jar, Tønsberg, Frisk Asker, Sandefjord Penguins, Jutul</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Sandefjord, Jutul Rød, Tønsberg Grå</t>
+          <t>Jar Svart, Tønsberg Rød, Frisk Asker 3, Sandefjord, Jutul Rød, Jar Lilla</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7514,47 +7514,47 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>07.02.2027</t>
+          <t>13.02.2027</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Sandefjord Penguins, Jutul</t>
+          <t>Jutul, Frisk Asker, Skien</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Jar Svart, Tønsberg Rød, Frisk Asker 3, Sandefjord, Jutul Rød, Jar Lilla</t>
+          <t>Jutul/Jar Kittens, Frisk Asker Orange, Skien</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Baerum ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7581,17 +7581,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Skien</t>
+          <t>Kongsberg, Frisk Asker, Tønsberg, Jutul</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens, Frisk Asker Orange, Skien</t>
+          <t>Kongsberg, Frisk Asker 3, Tønsberg Grå, Jutul Grønn</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7623,42 +7623,42 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker, Tønsberg, Jutul</t>
+          <t>Jar, Frisk Asker, Holmen, Jutul, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker 3, Tønsberg Grå, Jutul Grønn</t>
+          <t>Jar Svart, Frisk Asker 1, Holmen Hockey Blå, Frisk Asker 4, Jutul Rød, Holmen Hockey Hvit, Sandefjord, Jar Rød</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U8 Turnering — Jar Isforum</t>
+          <t>JU8 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen, Jutul, Sandefjord Penguins</t>
+          <t>Frisk Asker, Jar, Jutul, Skien</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Jar Svart, Frisk Asker 1, Holmen Hockey Blå, Frisk Asker 4, Jutul Rød, Holmen Hockey Hvit, Sandefjord, Jar Rød</t>
+          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7727,42 +7727,42 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JU8 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Skien</t>
+          <t>Ringerike, Tønsberg, Jar, Holmen</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul Kittens, Skien</t>
+          <t>Ringerike Svart, Ringerike Gul, Tønsberg Rød, Jar Oransje, Holmen Hockey Rød, Jar Grønn</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7779,42 +7779,42 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Ringerike, Tønsberg, Jar, Holmen</t>
+          <t>Jar, Ringerike, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Ringerike Svart, Ringerike Gul, Tønsberg Rød, Jar Oransje, Holmen Hockey Rød, Jar Grønn</t>
+          <t>Jar Hvit, Ringerike 2, Frisk Asker 2, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7826,47 +7826,47 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>13.02.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jar, Ringerike, Frisk Asker, Tønsberg</t>
+          <t>Jar, Holmen, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jar Hvit, Ringerike 2, Frisk Asker 2, Tønsberg Rød</t>
+          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Frisk Asker 5, Ringerike 4, Ringerike 2</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7883,42 +7883,42 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Frisk Asker, Ringerike</t>
+          <t>Holmen, Frisk Asker, Ringerike, Jar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Frisk Asker 5, Ringerike 4, Ringerike 2</t>
+          <t>Holmen Hockey Rød, Frisk Asker 3, Frisk Asker 4, Ringerike Gul, Jar Hvit, Jar Blå</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7935,42 +7935,42 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>U11 Turnering — Holmen ishall</t>
+          <t>U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Ringerike, Jar</t>
+          <t>Jar, Frisk Asker, Holmen</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Frisk Asker 3, Frisk Asker 4, Ringerike Gul, Jar Hvit, Jar Blå</t>
+          <t>Jar Svart, Frisk Asker 2, Holmen Hockey Rød, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -7987,42 +7987,42 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>U7 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Holmen</t>
+          <t>Jutul, Jar, Sandefjord Penguins, Holmen, Frisk Asker</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Jar Svart, Frisk Asker 2, Holmen Hockey Rød, Holmen Hockey Hvit</t>
+          <t>Jutul Rød, Jutul Hvit, Jar Svart, Sandefjord, Holmen Hockey Hvit, Jar Hvit, Frisk Asker 2, Jar Blå</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8039,42 +8039,42 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>U7 Turnering — Baerum ishall</t>
+          <t>U9 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Sandefjord Penguins, Holmen, Frisk Asker</t>
+          <t>Ringerike, Jutul, Frisk Asker, Holmen, Jar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jutul Hvit, Jar Svart, Sandefjord, Holmen Hockey Hvit, Jar Hvit, Frisk Asker 2, Jar Blå</t>
+          <t>Ringerike 1, Jutul Rød, Frisk Asker 3, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8086,47 +8086,47 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>20.02.2027</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>U9 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Frisk Asker, Jar, Ringerike, Kongsberg, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jutul Rød, Frisk Asker 3, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
+          <t>Frisk Asker 5, Jar Hvit, Ringerike 1, Kongsberg, Jutul Rød, Tønsberg</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8143,42 +8143,42 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U7 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Kongsberg, Jutul, Tønsberg</t>
+          <t>Holmen, Jar, Jutul, Frisk Asker, Tønsberg</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Frisk Asker 5, Jar Hvit, Ringerike 1, Kongsberg, Jutul Rød, Tønsberg</t>
+          <t>Holmen Hockey Hvit, Holmen Hockey Sort, Jar Grønn, Jutul Rød, Frisk Asker 2, Jar Rød, Frisk Asker 1, Tønsberg</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8195,42 +8195,42 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>U7 Turnering — Holmen ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Jutul, Frisk Asker, Tønsberg</t>
+          <t>Jutul, Kongsberg, Jar, Ringerike, Tønsberg, Skien, Holmen</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Holmen Hockey Sort, Jar Grønn, Jutul Rød, Frisk Asker 2, Jar Rød, Frisk Asker 1, Tønsberg</t>
+          <t>Jutul Gul, Jutul Hvit, Kongsberg, Jar Hvit, Ringerike 2, Tønsberg, Skien, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8247,42 +8247,42 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Jutul, Kongsberg, Jar, Ringerike, Tønsberg, Skien, Holmen</t>
+          <t>Jutul, Frisk Asker, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Jutul Gul, Jutul Hvit, Kongsberg, Jar Hvit, Ringerike 2, Tønsberg, Skien, Holmen Hockey Hvit</t>
+          <t>Jutul Hvit, Frisk Asker 3, Jar Rød, Holmen Hockey Rød, Ringerike 2, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>U10 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8309,17 +8309,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Jutul, Frisk Asker, Jar, Holmen, Ringerike</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Jutul Hvit, Frisk Asker 3, Jar Rød, Holmen Hockey Rød, Ringerike 2, Frisk Asker 2</t>
+          <t>Jar Hvit, Jar Rød, Frisk Asker Orange, Ringerike 1, Skien, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8351,42 +8351,42 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>U9 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Kongsberg, Frisk Asker, Jar, Jutul, Sandefjord Penguins, Ringerike</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Jar Hvit, Jar Rød, Frisk Asker Orange, Ringerike 1, Skien, Frisk Asker Svart</t>
+          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Sandefjord, Ringerike 1, Jar Hvit</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8403,42 +8403,42 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>U9 Turnering — Kongsberghallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker, Jar, Jutul, Sandefjord Penguins, Ringerike</t>
+          <t>Jar, Holmen, Ringerike, Tønsberg, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Sandefjord, Ringerike 1, Jar Hvit</t>
+          <t>Jar Oransje, Jar Lilla, Holmen Hockey Hvit, Ringerike Gul, Tønsberg Hvit, Sandefjord</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8450,47 +8450,47 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>20.02.2027</t>
+          <t>21.02.2027</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Ringerike, Tønsberg, Sandefjord Penguins</t>
+          <t>Ringerike, Jutul, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Jar Oransje, Jar Lilla, Holmen Hockey Hvit, Ringerike Gul, Tønsberg Hvit, Sandefjord</t>
+          <t>Ringerike 2, Ringerike 1, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8507,42 +8507,42 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Kongsberg/Tønsberg</t>
+          <t>Jar, Frisk Asker, Tønsberg, Ringerike, Holmen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Ringerike 2, Ringerike 1, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Jar Svart, Jar Blå, Frisk Asker 3, Tønsberg Grå, Ringerike Svart, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8559,42 +8559,42 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Tønsberg, Ringerike, Holmen</t>
+          <t>Frisk Asker, Jar, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Blå, Frisk Asker 3, Tønsberg Grå, Ringerike Svart, Holmen Hockey Hvit</t>
+          <t>Frisk Asker 3, Jar Rød, Tønsberg Hvit, Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -8611,42 +8611,42 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>U12 Turnering — Askerhallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Tønsberg, Holmen</t>
+          <t>Holmen, Frisk Asker, Jutul, Jar, Ringerike</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar Rød, Tønsberg Hvit, Holmen Hockey Rød</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Frisk Asker 2, Frisk Asker 4, Jutul Grønn, Jar Svart, Ringerike 1, Jar Blå</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -8663,42 +8663,42 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U9 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jutul, Jar, Ringerike</t>
+          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Skien, Frisk Asker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Frisk Asker 2, Frisk Asker 4, Jutul Grønn, Jar Svart, Ringerike 1, Jar Blå</t>
+          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Skien, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -8715,42 +8715,42 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>U9 Turnering — Tonsberghallen</t>
+          <t>U10 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Skien, Frisk Asker</t>
+          <t>Kongsberg, Jar, Ringerike, Frisk Asker, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Skien, Frisk Asker 2</t>
+          <t>Kongsberg, Jar Gul, Ringerike 3, Frisk Asker 1, Holmen Hockey Hvit, Jutul Rød</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -8762,47 +8762,47 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>21.02.2027</t>
+          <t>27.02.2027</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>U10 Turnering — Kongsberghallen</t>
+          <t>AVLYST: U12 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Ringerike, Frisk Asker, Holmen, Jutul</t>
+          <t>Frisk Asker, Jar, Tønsberg</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Gul, Ringerike 3, Frisk Asker 1, Holmen Hockey Hvit, Jutul Rød</t>
+          <t>Frisk Asker 3, Jar Hvit, Tønsberg Rød, Jar Blå</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -8819,42 +8819,42 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AVLYST: U12 Turnering — Askerhallen</t>
+          <t>AVLYST: U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Jar Isforum</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Tønsberg</t>
+          <t>Jar, Frisk Asker, Skien</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar Hvit, Tønsberg Rød, Jar Blå</t>
+          <t>Jar Lilla, Jar Rød, Jar Hvit, Frisk Asker 3, Skien, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -8866,12 +8866,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>27.02.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AVLYST: U11 Turnering — Jar Isforum</t>
+          <t>U11 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Skien</t>
+          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Jar Lilla, Jar Rød, Jar Hvit, Frisk Asker 3, Skien, Frisk Asker 2</t>
+          <t>Jar Gul, Jar Rød, Tønsberg Grå, Frisk Asker 2, Jutul Rød, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>U11 Turnering — Jar Isforum</t>
+          <t>JU10 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -8933,17 +8933,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Jar, Tønsberg, Frisk Asker, Jutul</t>
+          <t>Jar, Frisk Asker, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Jar Gul, Jar Rød, Tønsberg Grå, Frisk Asker 2, Jutul Rød, Frisk Asker 1</t>
+          <t>Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -8975,42 +8975,42 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Jar Isforum</t>
+          <t>JU12 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jar Isforum</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Ringerike, Skien</t>
+          <t>Ringerike, Frisk Asker</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Jar Rød, Jar Blå, Frisk Asker Orange, Ringerike 1, Skien</t>
+          <t>Ringerike 1, Ringerike 2, Frisk Asker Orange, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9027,42 +9027,42 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Schjongshallen</t>
+          <t>U10 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker</t>
+          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Ringerike 1, Ringerike 2, Frisk Asker Orange, Frisk Asker Svart</t>
+          <t>Frisk Asker 4, Jar Blå, Frisk Asker 1, Ringerike 4, Tønsberg, Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9079,42 +9079,42 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>U10 Turnering — Holmen ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Tønsberg, Holmen</t>
+          <t>Jutul, Jar, Ringerike, Holmen</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Blå, Frisk Asker 1, Ringerike 4, Tønsberg, Holmen Hockey Sort</t>
+          <t>Jutul Rød, Jar Svart, Ringerike 1, Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9131,42 +9131,42 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U9 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Ringerike, Holmen</t>
+          <t>Frisk Asker, Jar, Jutul, Kongsberg, Ringerike, Tønsberg</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jar Svart, Ringerike 1, Holmen Hockey Hvit</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Ringerike 1, Tønsberg</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9178,12 +9178,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>07.03.2027</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>U9 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9193,17 +9193,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Kongsberg, Ringerike, Tønsberg</t>
+          <t>Frisk Asker, Jar, Ringerike, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Ringerike 1, Tønsberg</t>
+          <t>Frisk Asker 2, Frisk Asker 6, Jar Svart, Ringerike 3, Holmen Hockey Hvit, Jutul Grønn</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9235,42 +9235,42 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Kongsberghallen</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Holmen, Jutul</t>
+          <t>Kongsberg, Jar, Ringerike</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Frisk Asker 6, Jar Svart, Ringerike 3, Holmen Hockey Hvit, Jutul Grønn</t>
+          <t>Kongsberg, Jar Rød, Ringerike 2, Jar Blå</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9287,42 +9287,42 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>U12 Turnering — Kongsberghallen</t>
+          <t>U8 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Ringerike</t>
+          <t>Holmen, Ringerike, Jar, Frisk Asker, Skien, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Rød, Ringerike 2, Jar Blå</t>
+          <t>Holmen Hockey Hvit, Ringerike 1, Jar Rød, Frisk Asker 3, Skien, Jutul Rød, Tønsberg, Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9339,42 +9339,42 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>U8 Turnering — Holmen ishall</t>
+          <t>U11 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Holmen, Ringerike, Jar, Frisk Asker, Skien, Jutul, Tønsberg</t>
+          <t>Frisk Asker, Jar, Ringerike, Sandefjord Penguins, Jutul</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Ringerike 1, Jar Rød, Frisk Asker 3, Skien, Jutul Rød, Tønsberg, Holmen Hockey Blå</t>
+          <t>Frisk Asker 4, Jar Svart, Ringerike Gul, Sandefjord, Jar Lilla, Jutul Rød</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9386,47 +9386,47 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>07.03.2027</t>
+          <t>13.03.2027</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>U11 Turnering — Askerhallen</t>
+          <t>U10 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Ringerike, Sandefjord Penguins, Jutul</t>
+          <t>Jutul, Jar, Frisk Asker, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Frisk Asker 4, Jar Svart, Ringerike Gul, Sandefjord, Jar Lilla, Jutul Rød</t>
+          <t>Jutul Rød, Jar Blå, Frisk Asker 2, Holmen Hockey Sort, Jar Hvit, Ringerike 2</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>U10 Turnering — Baerum ishall</t>
+          <t>JU12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9453,17 +9453,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Frisk Asker, Holmen, Ringerike</t>
+          <t>Jutul, Skien, Frisk Asker, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Jutul Rød, Jar Blå, Frisk Asker 2, Holmen Hockey Sort, Jar Hvit, Ringerike 2</t>
+          <t>Jutul/Jar Kittens, Skien, Frisk Asker Svart, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9495,42 +9495,42 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Baerum ishall</t>
+          <t>U11 Turnering — Bugården ishall</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Bugården ishall</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Jutul, Skien, Frisk Asker, Kongsberg/Tønsberg</t>
+          <t>Sandefjord Penguins, Jar, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens, Skien, Frisk Asker Svart, Kongsberg/Tønsberg</t>
+          <t>Sandefjord, Jar Gul, Frisk Asker 3, Ringerike Svart, Frisk Asker 4, Jar Lilla</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9713,12 +9713,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>AVLYST: U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>AVLYST: U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U11 Turnering — Baerum ishall</t>
+          <t>AVLYST: U11 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U12 Turnering — Jar Isforum</t>
+          <t>AVLYST: U12 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U9 Turnering — Baerum ishall</t>
+          <t>AVLYST: U9 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U9 Turnering — Jar Isforum</t>
+          <t>AVLYST: U9 Turnering — Jar Isforum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Frisk Asker, Ringerike</t>
+          <t>Jar, Holmen, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Frisk Asker 5, Ringerike 4, Ringerike 2</t>
+          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Ringerike 4, Ringerike 2</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7997,12 +7997,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>AVLYST: U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9453,12 +9453,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -841,12 +841,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Holmen, Frisk Asker, Jutul, Kongsberg, Ringerike, Skien</t>
+          <t>Holmen, Frisk Asker, Jutul, Kongsberg, Ringerike, Sandefjord Penguins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit, Frisk Asker 1, Holmen Hockey Rød, Jutul Rød, Kongsberg, Ringerike 1, Frisk Asker 4, Skien</t>
+          <t>Holmen Hockey Hvit, Frisk Asker 1, Holmen Hockey Rød, Jutul Rød, Kongsberg, Ringerike 1, Frisk Asker 4, Sandefjord</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Skien, Jar, Frisk Asker, Jutul, Ringerike</t>
+          <t>Jar, Frisk Asker, Jutul, Ringerike</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Skien, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
+          <t>Jar Svart, Jar Oransje, Jar Rød, Frisk Asker 2, Jutul Grønn, Ringerike Svart</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Holmen, Tønsberg, Ringerike, Sandefjord Penguins</t>
+          <t>Frisk Asker, Jar, Jutul, Holmen, Tønsberg, Ringerike, Skien</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Jar Hvit, Jutul Grønn, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Sandefjord</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Jar Hvit, Jutul Grønn, Holmen Hockey Hvit, Tønsberg, Ringerike 1, Skien</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Frisk Asker, Holmen, Ringerike, Jutul, Jar</t>
+          <t>Frisk Asker, Holmen, Ringerike, Jar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Jutul Rød, Jar Rød</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Holmen Hockey Rød, Ringerike 1, Frisk Asker 5, Jar Rød</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker, Jar, Jutul, Sandefjord Penguins, Ringerike</t>
+          <t>Kongsberg, Frisk Asker, Jar, Jutul, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Sandefjord, Ringerike 1, Jar Hvit</t>
+          <t>Kongsberg, Frisk Asker 2, Jar Rød, Jutul Rød, Jutul Hvit, Holmen Hockey Hvit, Ringerike 1, Jar Hvit</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Jar, Frisk Asker, Jutul, Tønsberg</t>
+          <t>Jar, Frisk Asker, Jutul, Skien, Tønsberg</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Jar Gul, Frisk Asker 1, Jar Hvit, Jutul Grønn, Jar Svart, Tønsberg Rød</t>
+          <t>Jar Gul, Frisk Asker 1, Jar Hvit, Jutul Grønn, Skien, Tønsberg Rød</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -2037,12 +2037,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Holmen, Jar, Frisk Asker, Skien, Jutul</t>
+          <t>Holmen, Jar, Frisk Asker, Ringerike, Jutul</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Skien, Jutul Grønn, Frisk Asker 2</t>
+          <t>Holmen Hockey Rød, Holmen Hockey Sort, Jar Blå, Jar Hvit, Frisk Asker 4, Ringerike 1, Jutul Grønn, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Frisk Asker, Holmen, Jar</t>
+          <t>Ringerike, Jutul, Skien, Holmen, Jar, Frisk Asker</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jutul Rød, Frisk Asker 3, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
+          <t>Ringerike 1, Jutul Rød, Skien, Holmen Hockey Rød, Jar Rød, Frisk Asker 1, Jar Hvit, Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Skien, Frisk Asker</t>
+          <t>Tønsberg, Holmen, Kongsberg, Jutul, Sandefjord Penguins, Frisk Asker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Skien, Frisk Asker 2</t>
+          <t>Tønsberg, Holmen Hockey Rød, Holmen Hockey Sort, Kongsberg, Jutul Grønn, Sandefjord, Frisk Asker 3, Frisk Asker 2</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Jutul, Kongsberg, Ringerike, Tønsberg</t>
+          <t>Frisk Asker, Jar, Jutul, Kongsberg, Skien, Tønsberg</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Ringerike 1, Tønsberg</t>
+          <t>Frisk Asker 1, Frisk Asker 4, Jar Blå, Jutul Hvit, Jar Rød, Kongsberg, Skien, Tønsberg</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -1678,7 +1678,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker Orange, Frisk Asker Svart, Jutul/Jar Kittens</t>
+          <t>Ringerike 2, Frisk Asker Orange, Ringerike 1, Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Holmen, Skien, Ringerike</t>
+          <t>Kongsberg, Jar, Holmen, Skien, Ringerike</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit, Jar Lilla, Jar Gul, Holmen Hockey Hvit, Skien, Ringerike Gul</t>
+          <t>Kongsberg, Jar Lilla, Jar Gul, Holmen Hockey Hvit, Skien, Ringerike Gul</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5989,12 +5989,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar, Frisk Asker, Holmen</t>
+          <t>Kongsberg, Sandefjord Penguins, Frisk Asker, Jar, Holmen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Kongsberg, Jar Blå, Frisk Asker 2, Jar Oransje, Holmen Hockey Hvit, Frisk Asker 1</t>
+          <t>Kongsberg, Sandefjord, Frisk Asker 2, Jar Oransje, Holmen Hockey Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tønsberg, Jar, Holmen, Kongsberg, Ringerike</t>
+          <t>Tønsberg, Jar, Holmen, Ringerike</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Kongsberg, Ringerike Svart, Jar Lilla</t>
+          <t>Tønsberg Rød, Jar Grønn, Holmen Hockey Rød, Tønsberg Hvit, Ringerike Svart, Jar Lilla</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Frisk Asker, Jar, Holmen, Sandefjord Penguins, Jutul, Tønsberg</t>
+          <t>Frisk Asker, Jar, Holmen, Jutul, Tønsberg</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Sandefjord, Jutul Rød, Tønsberg Grå</t>
+          <t>Frisk Asker 1, Jar Grønn, Holmen Hockey Rød, Jar Blå, Jutul Rød, Tønsberg Grå</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Ringerike, Jutul, Kongsberg/Tønsberg</t>
+          <t>Ringerike, Frisk Asker, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Ringerike 2, Ringerike 1, Jutul/Jar Kittens, Kongsberg/Tønsberg</t>
+          <t>Ringerike 2, Frisk Asker Svart, Frisk Asker Orange, Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker</t>
+          <t>Ringerike, Jutul, Frisk Asker</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Ringerike 1, Ringerike 2, Frisk Asker Orange, Frisk Asker Svart</t>
+          <t>Ringerike 1, Ringerike 2, Jutul/Jar Kittens, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">

--- a/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
+++ b/runs/20260918T135604Z-8d38f146/season_plan_spond.xlsx
@@ -7861,12 +7861,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jar, Holmen, Jutul, Ringerike</t>
+          <t>Jar, Holmen, Jutul</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Ringerike 4, Ringerike 2</t>
+          <t>Jar Svart, Jar Rød, Holmen Hockey Blå, Jutul Grønn, Holmen Hockey Sort, Jar Grønn</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
